--- a/从零开始学Slots/从零开始学Slots-08-基础篇-功能图标.xlsx
+++ b/从零开始学Slots/从零开始学Slots-08-基础篇-功能图标.xlsx
@@ -5766,6 +5766,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:I123" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -6420,5 +6423,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:M74" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-08-基础篇-功能图标.xlsx
+++ b/从零开始学Slots/从零开始学Slots-08-基础篇-功能图标.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="165">
   <si>
     <r>
       <rPr>
@@ -4899,7 +4899,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5026,6 +5026,10 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -6306,8 +6310,8 @@
       <c r="H46" s="14"/>
     </row>
     <row r="47" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="17" t="s">
-        <v>153</v>
+      <c r="A47" s="32">
+        <v>3</v>
       </c>
       <c r="B47" s="26" t="str">
         <f aca="false">IF(B21=10,"✓","✗")</f>

--- a/从零开始学Slots/从零开始学Slots-08-基础篇-功能图标.xlsx
+++ b/从零开始学Slots/从零开始学Slots-08-基础篇-功能图标.xlsx
@@ -4718,11 +4718,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="0.0000%"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
+    <numFmt numFmtId="168" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -4899,7 +4900,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5029,6 +5030,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" applyNumberFormat="1" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6092,7 +6097,7 @@
       <c r="A28" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="B28" s="22" t="n">
+      <c r="B28" s="33" t="n">
         <f aca="false">B27/B26</f>
         <v>0.000125</v>
       </c>
